--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.19023571286805</v>
+        <v>2.468413303341058</v>
       </c>
       <c r="D2" t="n">
-        <v>23.04886114323222</v>
+        <v>3.745439935775236</v>
       </c>
       <c r="E2" t="n">
-        <v>15.71314755974191</v>
+        <v>2.55338647845806</v>
       </c>
       <c r="F2" t="n">
-        <v>9.790751808912978</v>
+        <v>1.590997168948359</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.08998736642134</v>
+        <v>1.152122947043468</v>
       </c>
       <c r="D3" t="n">
-        <v>7.828637396232045</v>
+        <v>1.272153576887707</v>
       </c>
       <c r="E3" t="n">
-        <v>15.71314755974191</v>
+        <v>2.55338647845806</v>
       </c>
       <c r="F3" t="n">
-        <v>9.790751808912978</v>
+        <v>1.590997168948359</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.51336992610475</v>
+        <v>8.533422612992023</v>
       </c>
       <c r="D4" t="n">
-        <v>33.52692220397894</v>
+        <v>5.448124858146578</v>
       </c>
       <c r="E4" t="n">
-        <v>15.71314755974191</v>
+        <v>2.55338647845806</v>
       </c>
       <c r="F4" t="n">
-        <v>9.790751808912978</v>
+        <v>1.590997168948359</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.47311970379827</v>
+        <v>4.301881951867219</v>
       </c>
       <c r="D5" t="n">
-        <v>27.42607612513586</v>
+        <v>4.456737370334577</v>
       </c>
       <c r="E5" t="n">
-        <v>15.71314755974191</v>
+        <v>2.55338647845806</v>
       </c>
       <c r="F5" t="n">
-        <v>9.790751808912978</v>
+        <v>1.590997168948359</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.05516309001465</v>
+        <v>6.996464002127381</v>
       </c>
       <c r="D6" t="n">
-        <v>18.33712082089225</v>
+        <v>2.979782133394991</v>
       </c>
       <c r="E6" t="n">
-        <v>15.71314755974191</v>
+        <v>2.55338647845806</v>
       </c>
       <c r="F6" t="n">
-        <v>9.790751808912978</v>
+        <v>1.590997168948359</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.90978123947716</v>
+        <v>5.997839451415039</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42840564080156</v>
+        <v>6.082115916630253</v>
       </c>
       <c r="E7" t="n">
-        <v>15.71314755974191</v>
+        <v>2.55338647845806</v>
       </c>
       <c r="F7" t="n">
-        <v>9.790751808912978</v>
+        <v>1.590997168948359</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
